--- a/2022 data/excel_outputs/162_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/162_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="462">
   <si>
     <t>AC 162 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -31,7 +97,7 @@
     <t>PRIMARY PATHSHALA KAKSHA SANKHYA 1 BYOLI ISLAMABAAD</t>
   </si>
   <si>
-    <t>PRIMARY PATHSHALA KAKSHA SANKHYA ■ BYOLI ISLAMABAAD</t>
+    <t>BOOTH 3</t>
   </si>
   <si>
     <t>PRIMARY PHATHSHALA DHURANDHAR KHERA</t>
@@ -469,10 +535,13 @@
     <t>PRIMARY PATHSHALA BEHTA KAKSHA SANKHYA 1</t>
   </si>
   <si>
-    <t>PRIMARY PATHSHALA BEHTA KAKSHA SANKHYA ■</t>
-  </si>
-  <si>
-    <t>PRIMARY PATHSHALA BALLAPUR KAKSHA SANKHYA ■</t>
+    <t>BOOTH 149</t>
+  </si>
+  <si>
+    <t>BOOTH 150</t>
+  </si>
+  <si>
+    <t>BOOTH 151</t>
   </si>
   <si>
     <t>JUNIOR HIGH SCHOOL BALLAPUR KASHYA 1</t>
@@ -766,7 +835,7 @@
     <t>PRIMARY PATHSHALA HARIYAWAR KASHYA SANKHYA 1</t>
   </si>
   <si>
-    <t>PRIMARY PATHSHALA HARIYAWAR KASHYA SANKHYA ■</t>
+    <t>BOOTH 249</t>
   </si>
   <si>
     <t>PRIMARY PHATHSHALA SALARI KHERA</t>
@@ -796,7 +865,10 @@
     <t>JAWAHAR LAL NEHRU INTER COLLEGE PHTEHPUR CHAURSHI SAHARI KASHA SANKHYA 1</t>
   </si>
   <si>
-    <t>JAWAHAR LAL NEHRU INTER COLLEGE PHTEHPUR CHAURSHI SAHARI KASHA SANKHYA ■</t>
+    <t>BOOTH 259</t>
+  </si>
+  <si>
+    <t>BOOTH 260</t>
   </si>
   <si>
     <t>JAWAHAR LAL NEHRU INTER COLLEGE PHTEHPUR CHAURSHI SAHARI KASHA SANKHYA 4</t>
@@ -928,7 +1000,7 @@
     <t>JUNIOR HIGH SCHOOL RAJEPUR KASHYA SANKHYA 1</t>
   </si>
   <si>
-    <t>JUNIOR HIGH SCHOOL RAJEPUR KASHYA SANKHYA ■</t>
+    <t>BOOTH 304</t>
   </si>
   <si>
     <t>JUNIOR HIGH SCHOOL KAMLAPUR KASHYA SANKHYA 1</t>
@@ -1334,8 +1406,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1351,7 +1431,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1359,12 +1439,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1663,79 +1761,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D2" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="E2" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="F2" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="G2" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="H2" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="I2" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="J2" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="K2" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="L2" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="M2" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="N2" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="O2" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="P2" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="Q2" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="R2" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="S2" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="T2" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="U2" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="V2" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="W2" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1743,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>806</v>
@@ -1814,7 +1978,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>1061</v>
@@ -1885,7 +2049,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>950</v>
@@ -1956,7 +2120,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>1122</v>
@@ -2027,7 +2191,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1136</v>
@@ -2098,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>748</v>
@@ -2169,7 +2333,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>1026</v>
@@ -2240,7 +2404,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>780</v>
@@ -2311,7 +2475,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>765</v>
@@ -2382,7 +2546,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1059</v>
@@ -2453,7 +2617,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>601</v>
@@ -2524,7 +2688,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>607</v>
@@ -2595,7 +2759,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1068</v>
@@ -2666,7 +2830,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>755</v>
@@ -2737,7 +2901,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1098</v>
@@ -2808,7 +2972,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>661</v>
@@ -2879,7 +3043,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>1140</v>
@@ -2950,7 +3114,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>651</v>
@@ -3021,7 +3185,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>636</v>
@@ -3092,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>584</v>
@@ -3163,7 +3327,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>532</v>
@@ -3234,7 +3398,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>793</v>
@@ -3305,7 +3469,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>996</v>
@@ -3376,7 +3540,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>815</v>
@@ -3447,7 +3611,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>1091</v>
@@ -3518,7 +3682,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>667</v>
@@ -3589,7 +3753,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>619</v>
@@ -3660,7 +3824,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>830</v>
@@ -3731,7 +3895,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>727</v>
@@ -3802,7 +3966,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>571</v>
@@ -3873,7 +4037,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1031</v>
@@ -3944,7 +4108,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>812</v>
@@ -4015,7 +4179,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>639</v>
@@ -4086,7 +4250,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>978</v>
@@ -4157,7 +4321,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>703</v>
@@ -4228,7 +4392,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>1005</v>
@@ -4299,7 +4463,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>829</v>
@@ -4370,7 +4534,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>655</v>
@@ -4441,7 +4605,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>708</v>
@@ -4512,7 +4676,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>656</v>
@@ -4583,7 +4747,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>658</v>
@@ -4654,7 +4818,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>789</v>
@@ -4725,7 +4889,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>688</v>
@@ -4796,7 +4960,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>867</v>
@@ -4867,7 +5031,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>1190</v>
@@ -4938,7 +5102,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>370</v>
@@ -5009,7 +5173,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>759</v>
@@ -5080,7 +5244,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>702</v>
@@ -5151,7 +5315,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>822</v>
@@ -5222,7 +5386,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>876</v>
@@ -5293,7 +5457,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>488</v>
@@ -5364,7 +5528,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>843</v>
@@ -5435,7 +5599,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>967</v>
@@ -5506,7 +5670,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>513</v>
@@ -5577,7 +5741,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>746</v>
@@ -5648,7 +5812,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>688</v>
@@ -5719,7 +5883,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>689</v>
@@ -5790,7 +5954,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>783</v>
@@ -5861,7 +6025,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>1061</v>
@@ -5932,7 +6096,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>994</v>
@@ -6003,7 +6167,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>601</v>
@@ -6074,7 +6238,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>361</v>
@@ -6145,7 +6309,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>519</v>
@@ -6216,7 +6380,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>1031</v>
@@ -6287,7 +6451,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>1164</v>
@@ -6358,7 +6522,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>461</v>
@@ -6429,7 +6593,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>969</v>
@@ -6500,7 +6664,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>609</v>
@@ -6571,7 +6735,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>911</v>
@@ -6642,7 +6806,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>1037</v>
@@ -6713,7 +6877,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>1147</v>
@@ -6784,7 +6948,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>1070</v>
@@ -6855,7 +7019,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>1034</v>
@@ -6926,7 +7090,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>970</v>
@@ -6997,7 +7161,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>883</v>
@@ -7068,7 +7232,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>937</v>
@@ -7139,7 +7303,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>871</v>
@@ -7210,7 +7374,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>775</v>
@@ -7281,7 +7445,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>1124</v>
@@ -7352,7 +7516,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1117</v>
@@ -7423,7 +7587,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1025</v>
@@ -7494,7 +7658,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>1162</v>
@@ -7565,7 +7729,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>575</v>
@@ -7636,7 +7800,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>931</v>
@@ -7707,7 +7871,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>1106</v>
@@ -7778,7 +7942,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>977</v>
@@ -7849,7 +8013,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>469</v>
@@ -7920,7 +8084,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>1050</v>
@@ -7991,7 +8155,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>1053</v>
@@ -8062,7 +8226,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>875</v>
@@ -8133,7 +8297,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>739</v>
@@ -8204,7 +8368,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>963</v>
@@ -8275,7 +8439,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>617</v>
@@ -8346,7 +8510,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>945</v>
@@ -8417,7 +8581,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>874</v>
@@ -8488,7 +8652,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>847</v>
@@ -8559,7 +8723,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>1013</v>
@@ -8630,7 +8794,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>917</v>
@@ -8701,7 +8865,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>1152</v>
@@ -8772,7 +8936,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>441</v>
@@ -8843,7 +9007,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>456</v>
@@ -8914,7 +9078,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>609</v>
@@ -8985,7 +9149,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>637</v>
@@ -9056,7 +9220,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>685</v>
@@ -9127,7 +9291,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>1138</v>
@@ -9198,7 +9362,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>1075</v>
@@ -9269,7 +9433,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>1040</v>
@@ -9340,7 +9504,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>1162</v>
@@ -9411,7 +9575,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>959</v>
@@ -9482,7 +9646,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>392</v>
@@ -9553,7 +9717,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>1098</v>
@@ -9624,7 +9788,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>949</v>
@@ -9695,7 +9859,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>581</v>
@@ -9766,7 +9930,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>1003</v>
@@ -9837,7 +10001,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>685</v>
@@ -9908,7 +10072,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>1085</v>
@@ -9979,7 +10143,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>1075</v>
@@ -10050,7 +10214,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>1117</v>
@@ -10121,7 +10285,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>1049</v>
@@ -10192,7 +10356,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>1107</v>
@@ -10263,7 +10427,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>1041</v>
@@ -10334,7 +10498,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>700</v>
@@ -10405,7 +10569,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>1016</v>
@@ -10476,7 +10640,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>578</v>
@@ -10547,7 +10711,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>387</v>
@@ -10618,7 +10782,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>956</v>
@@ -10689,7 +10853,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>937</v>
@@ -10760,7 +10924,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>1072</v>
@@ -10831,7 +10995,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>1107</v>
@@ -10902,7 +11066,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>1175</v>
@@ -10973,7 +11137,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>1046</v>
@@ -11044,7 +11208,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>989</v>
@@ -11115,7 +11279,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>1094</v>
@@ -11186,7 +11350,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>760</v>
@@ -11257,7 +11421,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>780</v>
@@ -11328,7 +11492,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>850</v>
@@ -11399,7 +11563,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>1191</v>
@@ -11470,7 +11634,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>856</v>
@@ -11541,7 +11705,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>999</v>
@@ -11612,7 +11776,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>1030</v>
@@ -11683,7 +11847,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>738</v>
@@ -11754,7 +11918,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>694</v>
@@ -11825,7 +11989,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>899</v>
@@ -11896,7 +12060,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>910</v>
@@ -11967,7 +12131,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>743</v>
@@ -12038,7 +12202,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>868</v>
@@ -12109,7 +12273,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>655</v>
@@ -12180,7 +12344,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>1044</v>
@@ -12251,7 +12415,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>670</v>
@@ -12322,7 +12486,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>893</v>
@@ -12393,7 +12557,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>821</v>
@@ -12464,7 +12628,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>854</v>
@@ -12535,7 +12699,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>631</v>
@@ -12606,7 +12770,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>1189</v>
@@ -12677,7 +12841,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>287</v>
@@ -12748,7 +12912,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1104</v>
@@ -12819,7 +12983,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>1068</v>
@@ -12890,7 +13054,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>159</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>987</v>
@@ -12961,7 +13125,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>627</v>
@@ -13032,7 +13196,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>856</v>
@@ -13103,7 +13267,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>890</v>
@@ -13174,7 +13338,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>884</v>
@@ -13245,7 +13409,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>1034</v>
@@ -13316,7 +13480,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>1036</v>
@@ -13387,7 +13551,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>680</v>
@@ -13458,7 +13622,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>620</v>
@@ -13529,7 +13693,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>677</v>
@@ -13600,7 +13764,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>861</v>
@@ -13671,7 +13835,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>170</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>1081</v>
@@ -13742,7 +13906,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>830</v>
@@ -13813,7 +13977,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>1177</v>
@@ -13884,7 +14048,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>401</v>
@@ -13955,7 +14119,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>794</v>
@@ -14026,7 +14190,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>732</v>
@@ -14097,7 +14261,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>865</v>
@@ -14168,7 +14332,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>669</v>
@@ -14239,7 +14403,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>939</v>
@@ -14310,7 +14474,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>355</v>
@@ -14381,7 +14545,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>449</v>
@@ -14452,7 +14616,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>1039</v>
@@ -14523,7 +14687,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>1045</v>
@@ -14594,7 +14758,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>846</v>
@@ -14665,7 +14829,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>184</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>911</v>
@@ -14736,7 +14900,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>1103</v>
@@ -14807,7 +14971,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>869</v>
@@ -14878,7 +15042,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>941</v>
@@ -14949,7 +15113,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>712</v>
@@ -15020,7 +15184,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>853</v>
@@ -15091,7 +15255,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>752</v>
@@ -15162,7 +15326,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>789</v>
@@ -15233,7 +15397,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>481</v>
@@ -15304,7 +15468,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>1096</v>
@@ -15375,7 +15539,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>194</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>851</v>
@@ -15446,7 +15610,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>1199</v>
@@ -15517,7 +15681,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>837</v>
@@ -15588,7 +15752,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>648</v>
@@ -15659,7 +15823,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>1140</v>
@@ -15730,7 +15894,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>947</v>
@@ -15801,7 +15965,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>200</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>1020</v>
@@ -15872,7 +16036,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>914</v>
@@ -15943,7 +16107,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>1112</v>
@@ -16014,7 +16178,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>812</v>
@@ -16085,7 +16249,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>942</v>
@@ -16156,7 +16320,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>730</v>
@@ -16227,7 +16391,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>1072</v>
@@ -16298,7 +16462,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>877</v>
@@ -16369,7 +16533,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>658</v>
@@ -16440,7 +16604,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>847</v>
@@ -16511,7 +16675,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>908</v>
@@ -16582,7 +16746,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>1107</v>
@@ -16653,7 +16817,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>916</v>
@@ -16724,7 +16888,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>1134</v>
@@ -16795,7 +16959,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>939</v>
@@ -16866,7 +17030,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>944</v>
@@ -16937,7 +17101,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>1105</v>
@@ -17008,7 +17172,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>1146</v>
@@ -17079,7 +17243,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>957</v>
@@ -17150,7 +17314,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>1086</v>
@@ -17221,7 +17385,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>706</v>
@@ -17292,7 +17456,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>1047</v>
@@ -17363,7 +17527,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>663</v>
@@ -17434,7 +17598,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>1106</v>
@@ -17505,7 +17669,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>1180</v>
@@ -17576,7 +17740,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>1127</v>
@@ -17647,7 +17811,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>1131</v>
@@ -17718,7 +17882,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>864</v>
@@ -17789,7 +17953,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>1103</v>
@@ -17860,7 +18024,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>905</v>
@@ -17931,7 +18095,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>847</v>
@@ -18002,7 +18166,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>1084</v>
@@ -18073,7 +18237,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>900</v>
@@ -18144,7 +18308,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>1132</v>
@@ -18215,7 +18379,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>985</v>
@@ -18286,7 +18450,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>728</v>
@@ -18357,7 +18521,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>741</v>
@@ -18428,7 +18592,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>482</v>
@@ -18499,7 +18663,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>773</v>
@@ -18570,7 +18734,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>778</v>
@@ -18641,7 +18805,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>496</v>
@@ -18712,7 +18876,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>840</v>
@@ -18783,7 +18947,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>616</v>
@@ -18854,7 +19018,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>614</v>
@@ -18925,7 +19089,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>1148</v>
@@ -18996,7 +19160,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>1174</v>
@@ -19067,7 +19231,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>799</v>
@@ -19138,7 +19302,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>734</v>
@@ -19209,7 +19373,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>935</v>
@@ -19280,7 +19444,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>469</v>
@@ -19351,7 +19515,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>969</v>
@@ -19422,7 +19586,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>966</v>
@@ -19493,7 +19657,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>1221</v>
@@ -19564,7 +19728,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>446</v>
@@ -19635,7 +19799,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>756</v>
@@ -19706,7 +19870,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>800</v>
@@ -19777,7 +19941,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>813</v>
@@ -19848,7 +20012,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>720</v>
@@ -19919,7 +20083,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>1177</v>
@@ -19990,7 +20154,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>1001</v>
@@ -20061,7 +20225,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>810</v>
@@ -20132,7 +20296,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>1155</v>
@@ -20203,7 +20367,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>1041</v>
@@ -20274,7 +20438,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>882</v>
@@ -20345,7 +20509,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>1115</v>
@@ -20416,7 +20580,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>1171</v>
@@ -20487,7 +20651,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>533</v>
@@ -20558,7 +20722,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>639</v>
@@ -20629,7 +20793,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>668</v>
@@ -20700,7 +20864,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>787</v>
@@ -20771,7 +20935,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>269</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>927</v>
@@ -20842,7 +21006,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>826</v>
@@ -20913,7 +21077,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>271</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>1197</v>
@@ -20984,7 +21148,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>1060</v>
@@ -21055,7 +21219,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>966</v>
@@ -21126,7 +21290,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>619</v>
@@ -21197,7 +21361,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>809</v>
@@ -21268,7 +21432,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>397</v>
@@ -21339,7 +21503,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>953</v>
@@ -21410,7 +21574,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>278</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>642</v>
@@ -21481,7 +21645,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>1104</v>
@@ -21552,7 +21716,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>576</v>
@@ -21623,7 +21787,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>674</v>
@@ -21694,7 +21858,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>645</v>
@@ -21765,7 +21929,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>936</v>
@@ -21836,7 +22000,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>1052</v>
@@ -21907,7 +22071,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>993</v>
@@ -21978,7 +22142,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>710</v>
@@ -22049,7 +22213,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>287</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>957</v>
@@ -22120,7 +22284,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>288</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>604</v>
@@ -22191,7 +22355,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>678</v>
@@ -22262,7 +22426,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>290</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>994</v>
@@ -22333,7 +22497,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>776</v>
@@ -22404,7 +22568,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>596</v>
@@ -22475,7 +22639,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>293</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>712</v>
@@ -22546,7 +22710,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>294</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>773</v>
@@ -22617,7 +22781,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>295</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>765</v>
@@ -22688,7 +22852,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>296</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>809</v>
@@ -22759,7 +22923,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>689</v>
@@ -22830,7 +22994,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>618</v>
@@ -22901,7 +23065,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>299</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>771</v>
@@ -22972,7 +23136,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>300</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>511</v>
@@ -23043,7 +23207,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>500</v>
@@ -23114,7 +23278,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>302</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>514</v>
@@ -23185,7 +23349,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>303</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>1089</v>
@@ -23256,7 +23420,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>1105</v>
@@ -23327,7 +23491,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>305</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>765</v>
@@ -23398,7 +23562,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>306</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>581</v>
@@ -23469,7 +23633,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>836</v>
@@ -23540,7 +23704,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>308</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>921</v>
@@ -23611,7 +23775,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>309</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>1085</v>
@@ -23682,7 +23846,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>952</v>
@@ -23753,7 +23917,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>311</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>687</v>
@@ -23824,7 +23988,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>645</v>
@@ -23895,7 +24059,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>840</v>
@@ -23966,7 +24130,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>314</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>490</v>
@@ -24037,7 +24201,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>1002</v>
@@ -24108,7 +24272,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>808</v>
@@ -24179,7 +24343,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>317</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>577</v>
@@ -24250,7 +24414,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>318</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>599</v>
@@ -24321,7 +24485,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>936</v>
@@ -24392,7 +24556,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>963</v>
@@ -24463,7 +24627,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>1135</v>
@@ -24534,7 +24698,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>848</v>
@@ -24605,7 +24769,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>704</v>
@@ -24676,7 +24840,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>1048</v>
@@ -24747,7 +24911,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>900</v>
@@ -24818,7 +24982,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>461</v>
@@ -24889,7 +25053,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>1177</v>
@@ -24960,7 +25124,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>873</v>
@@ -25031,7 +25195,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>724</v>
@@ -25102,7 +25266,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>1006</v>
@@ -25173,7 +25337,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>982</v>
@@ -25244,7 +25408,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>698</v>
@@ -25315,7 +25479,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>502</v>
@@ -25386,7 +25550,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>959</v>
@@ -25457,7 +25621,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>881</v>
@@ -25528,7 +25692,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>1050</v>
@@ -25599,7 +25763,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>793</v>
@@ -25670,7 +25834,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>529</v>
@@ -25741,7 +25905,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>714</v>
@@ -25812,7 +25976,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>821</v>
@@ -25883,7 +26047,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>1122</v>
@@ -25954,7 +26118,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>735</v>
@@ -26025,7 +26189,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>794</v>
@@ -26096,7 +26260,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>1019</v>
@@ -26167,7 +26331,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>898</v>
@@ -26238,7 +26402,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>406</v>
@@ -26309,7 +26473,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>1171</v>
@@ -26380,7 +26544,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>636</v>
@@ -26451,7 +26615,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>881</v>
@@ -26522,7 +26686,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>861</v>
@@ -26593,7 +26757,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>1132</v>
@@ -26664,7 +26828,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>1148</v>
@@ -26735,7 +26899,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>1118</v>
@@ -26806,7 +26970,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>869</v>
@@ -26877,7 +27041,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>1010</v>
@@ -26948,7 +27112,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>866</v>
@@ -27019,7 +27183,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>742</v>
@@ -27090,7 +27254,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>788</v>
@@ -27161,7 +27325,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>640</v>
@@ -27232,7 +27396,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>617</v>
@@ -27303,7 +27467,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>1024</v>
@@ -27374,7 +27538,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>862</v>
@@ -27445,7 +27609,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>1005</v>
@@ -27516,7 +27680,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>1169</v>
@@ -27587,7 +27751,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>1089</v>
@@ -27658,7 +27822,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>980</v>
@@ -27729,7 +27893,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>871</v>
@@ -27800,7 +27964,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>901</v>
@@ -27871,7 +28035,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>799</v>
@@ -27942,7 +28106,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>890</v>
@@ -28013,7 +28177,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>775</v>
@@ -28084,7 +28248,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>1011</v>
@@ -28155,7 +28319,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>1011</v>
@@ -28226,7 +28390,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>430</v>
@@ -28297,7 +28461,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>441</v>
@@ -28368,7 +28532,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>691</v>
@@ -28439,7 +28603,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>645</v>
@@ -28510,7 +28674,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>771</v>
@@ -28581,7 +28745,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>547</v>
@@ -28652,7 +28816,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>362</v>
@@ -28723,7 +28887,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>1121</v>
@@ -28794,7 +28958,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>873</v>
@@ -28865,7 +29029,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>832</v>
@@ -28936,7 +29100,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>616</v>
@@ -29007,7 +29171,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>803</v>
@@ -29078,7 +29242,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>816</v>
@@ -29149,7 +29313,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="C389">
         <v>778</v>
@@ -29220,7 +29384,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="C390">
         <v>1094</v>
@@ -29291,7 +29455,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="C391">
         <v>1164</v>
@@ -29362,7 +29526,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="C392">
         <v>1118</v>
@@ -29433,7 +29597,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="C393">
         <v>901</v>
@@ -29504,7 +29668,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="C394">
         <v>592</v>
@@ -29575,7 +29739,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="C395">
         <v>1066</v>
@@ -29646,7 +29810,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="C396">
         <v>1204</v>
@@ -29717,7 +29881,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="C397">
         <v>1148</v>
@@ -29788,7 +29952,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="C398">
         <v>752</v>
@@ -29859,7 +30023,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="C399">
         <v>743</v>
@@ -29930,7 +30094,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="C400">
         <v>892</v>
@@ -30001,7 +30165,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="C401">
         <v>1002</v>
@@ -30072,7 +30236,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="C402">
         <v>844</v>
@@ -30143,7 +30307,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="C403">
         <v>754</v>
@@ -30214,7 +30378,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="C404">
         <v>1038</v>
@@ -30285,7 +30449,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="C405">
         <v>996</v>
@@ -30356,7 +30520,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="C406">
         <v>971</v>
@@ -30427,7 +30591,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="C407">
         <v>973</v>
@@ -30498,7 +30662,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="C408">
         <v>801</v>
@@ -30569,7 +30733,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="C409">
         <v>902</v>
@@ -30640,7 +30804,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="C410">
         <v>838</v>
@@ -30711,7 +30875,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="C411">
         <v>1150</v>
@@ -30782,7 +30946,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="C412">
         <v>1085</v>
@@ -30853,7 +31017,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="C413">
         <v>984</v>
@@ -30924,7 +31088,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="C414">
         <v>782</v>
@@ -30995,7 +31159,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C415">
         <v>942</v>
@@ -31066,7 +31230,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="C416">
         <v>956</v>
@@ -31137,7 +31301,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="C417">
         <v>1047</v>
@@ -31208,7 +31372,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="C418">
         <v>1167</v>
